--- a/00_Documentos/Sistematización figuras y variables - Proyecto Provincias-.xlsx
+++ b/00_Documentos/Sistematización figuras y variables - Proyecto Provincias-.xlsx
@@ -4325,7 +4325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J288"/>
+  <dimension ref="A1:J306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90.42578125" bestFit="1" customWidth="1" style="12" min="2" max="2"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Requiere población desagregada por sexo; insumo por confirmar (candidato: poblacion_municipal_total_2025_dicc.xlsx).</t>
+          <t>Población desagregada por sexo (suma de quinquenios), hoja Rangos_Quintenios de POBLACION MUNICIPAL.xlsx; implementado en 02_Demografia.do (bloque 2.2). Consistencia: pob_masc=Σ h_edad_*, pob_fem=Σ m_edad_*.</t>
         </is>
       </c>
     </row>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Requiere población desagregada por sexo; insumo por confirmar (candidato: poblacion_municipal_total_2025_dicc.xlsx).</t>
+          <t>Población desagregada por sexo (suma de quinquenios), hoja Rangos_Quintenios de POBLACION MUNICIPAL.xlsx; implementado en 02_Demografia.do (bloque 2.2). Consistencia: pob_masc=Σ h_edad_*, pob_fem=Σ m_edad_*.</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Categórico</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Categórica</t>
+          <t>Discreta</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -18892,6 +18892,942 @@
       <c r="J288" t="inlineStr">
         <is>
           <t>Llave transversal: código DANE del municipio (llave de cruce en todo el flujo), presente en (casi) todas las figuras municipales; por eso Figura queda vacía. Variantes en algunos do-files: cmpio, Codigo/Código, Divipola, cod_mun, CODMPIO, COD_MPIO, DIVIPOLA, cod_dane.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>h_edad_0_9</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Población masculina por grupo de edad: 0 a 9 años</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Discreta</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>personas</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>1985-2035</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Distribución por género y grupos de edad en la PAP</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>POBLACION MUNICIPAL.xlsx</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>Desagregación edad × sexo (banda de 10 años) para la pirámide poblacional; hoja Rangos_Quintenios de POBLACION MUNICIPAL.xlsx (02_Demografia.do, bloque 2.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>h_edad_10_19</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Población masculina por grupo de edad: 10 a 19 años</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Discreta</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>personas</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>1985-2035</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Distribución por género y grupos de edad en la PAP</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>POBLACION MUNICIPAL.xlsx</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>Desagregación edad × sexo (banda de 10 años) para la pirámide poblacional; hoja Rangos_Quintenios de POBLACION MUNICIPAL.xlsx (02_Demografia.do, bloque 2.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>h_edad_20_29</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Población masculina por grupo de edad: 20 a 29 años</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Discreta</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>personas</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>1985-2035</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Distribución por género y grupos de edad en la PAP</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>POBLACION MUNICIPAL.xlsx</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>Desagregación edad × sexo (banda de 10 años) para la pirámide poblacional; hoja Rangos_Quintenios de POBLACION MUNICIPAL.xlsx (02_Demografia.do, bloque 2.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>h_edad_30_39</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Población masculina por grupo de edad: 30 a 39 años</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Discreta</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>personas</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>1985-2035</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Distribución por género y grupos de edad en la PAP</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>POBLACION MUNICIPAL.xlsx</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>Desagregación edad × sexo (banda de 10 años) para la pirámide poblacional; hoja Rangos_Quintenios de POBLACION MUNICIPAL.xlsx (02_Demografia.do, bloque 2.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>h_edad_40_49</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Población masculina por grupo de edad: 40 a 49 años</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Discreta</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>personas</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>1985-2035</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Distribución por género y grupos de edad en la PAP</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>POBLACION MUNICIPAL.xlsx</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>Desagregación edad × sexo (banda de 10 años) para la pirámide poblacional; hoja Rangos_Quintenios de POBLACION MUNICIPAL.xlsx (02_Demografia.do, bloque 2.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>h_edad_50_59</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Población masculina por grupo de edad: 50 a 59 años</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Discreta</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>personas</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>1985-2035</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Distribución por género y grupos de edad en la PAP</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>POBLACION MUNICIPAL.xlsx</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>Desagregación edad × sexo (banda de 10 años) para la pirámide poblacional; hoja Rangos_Quintenios de POBLACION MUNICIPAL.xlsx (02_Demografia.do, bloque 2.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>h_edad_60_69</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Población masculina por grupo de edad: 60 a 69 años</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Discreta</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>personas</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>1985-2035</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Distribución por género y grupos de edad en la PAP</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>POBLACION MUNICIPAL.xlsx</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>Desagregación edad × sexo (banda de 10 años) para la pirámide poblacional; hoja Rangos_Quintenios de POBLACION MUNICIPAL.xlsx (02_Demografia.do, bloque 2.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>h_edad_70_79</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Población masculina por grupo de edad: 70 a 79 años</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Discreta</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>personas</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>1985-2035</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Distribución por género y grupos de edad en la PAP</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>POBLACION MUNICIPAL.xlsx</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>Desagregación edad × sexo (banda de 10 años) para la pirámide poblacional; hoja Rangos_Quintenios de POBLACION MUNICIPAL.xlsx (02_Demografia.do, bloque 2.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>h_edad_80_mas</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Población masculina por grupo de edad: 80 o más años</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Discreta</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>personas</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>1985-2035</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Distribución por género y grupos de edad en la PAP</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>POBLACION MUNICIPAL.xlsx</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>Desagregación edad × sexo (banda de 10 años) para la pirámide poblacional; hoja Rangos_Quintenios de POBLACION MUNICIPAL.xlsx (02_Demografia.do, bloque 2.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>m_edad_0_9</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Población femenina por grupo de edad: 0 a 9 años</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Discreta</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>personas</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>1985-2035</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Distribución por género y grupos de edad en la PAP</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>POBLACION MUNICIPAL.xlsx</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>Desagregación edad × sexo (banda de 10 años) para la pirámide poblacional; hoja Rangos_Quintenios de POBLACION MUNICIPAL.xlsx (02_Demografia.do, bloque 2.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>m_edad_10_19</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Población femenina por grupo de edad: 10 a 19 años</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Discreta</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>personas</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>1985-2035</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Distribución por género y grupos de edad en la PAP</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>POBLACION MUNICIPAL.xlsx</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>Desagregación edad × sexo (banda de 10 años) para la pirámide poblacional; hoja Rangos_Quintenios de POBLACION MUNICIPAL.xlsx (02_Demografia.do, bloque 2.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>m_edad_20_29</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Población femenina por grupo de edad: 20 a 29 años</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Discreta</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>personas</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>1985-2035</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Distribución por género y grupos de edad en la PAP</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>POBLACION MUNICIPAL.xlsx</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>Desagregación edad × sexo (banda de 10 años) para la pirámide poblacional; hoja Rangos_Quintenios de POBLACION MUNICIPAL.xlsx (02_Demografia.do, bloque 2.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>m_edad_30_39</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Población femenina por grupo de edad: 30 a 39 años</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Discreta</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>personas</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>1985-2035</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Distribución por género y grupos de edad en la PAP</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>POBLACION MUNICIPAL.xlsx</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>Desagregación edad × sexo (banda de 10 años) para la pirámide poblacional; hoja Rangos_Quintenios de POBLACION MUNICIPAL.xlsx (02_Demografia.do, bloque 2.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>m_edad_40_49</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Población femenina por grupo de edad: 40 a 49 años</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Discreta</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>personas</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>1985-2035</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Distribución por género y grupos de edad en la PAP</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>POBLACION MUNICIPAL.xlsx</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>Desagregación edad × sexo (banda de 10 años) para la pirámide poblacional; hoja Rangos_Quintenios de POBLACION MUNICIPAL.xlsx (02_Demografia.do, bloque 2.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>m_edad_50_59</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Población femenina por grupo de edad: 50 a 59 años</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Discreta</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>personas</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>1985-2035</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Distribución por género y grupos de edad en la PAP</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>POBLACION MUNICIPAL.xlsx</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>Desagregación edad × sexo (banda de 10 años) para la pirámide poblacional; hoja Rangos_Quintenios de POBLACION MUNICIPAL.xlsx (02_Demografia.do, bloque 2.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>m_edad_60_69</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Población femenina por grupo de edad: 60 a 69 años</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Discreta</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>personas</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>1985-2035</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Distribución por género y grupos de edad en la PAP</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>POBLACION MUNICIPAL.xlsx</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>Desagregación edad × sexo (banda de 10 años) para la pirámide poblacional; hoja Rangos_Quintenios de POBLACION MUNICIPAL.xlsx (02_Demografia.do, bloque 2.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>m_edad_70_79</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Población femenina por grupo de edad: 70 a 79 años</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Discreta</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>personas</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>1985-2035</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Distribución por género y grupos de edad en la PAP</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>POBLACION MUNICIPAL.xlsx</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>Desagregación edad × sexo (banda de 10 años) para la pirámide poblacional; hoja Rangos_Quintenios de POBLACION MUNICIPAL.xlsx (02_Demografia.do, bloque 2.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>m_edad_80_mas</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Población femenina por grupo de edad: 80 o más años</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Discreta</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>personas</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>1985-2035</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Distribución por género y grupos de edad en la PAP</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>POBLACION MUNICIPAL.xlsx</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>Desagregación edad × sexo (banda de 10 años) para la pirámide poblacional; hoja Rangos_Quintenios de POBLACION MUNICIPAL.xlsx (02_Demografia.do, bloque 2.2).</t>
         </is>
       </c>
     </row>
